--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-visualization-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-visualization-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Waterfall Chart (Biểu đồ thác nước) cực kỳ hữu ích trong tài chính để giải thích sự thay đổi từ trạng thái A sang trạng thái B thông qua các khoản cộng/trừ trung gian.</v>
       </c>
       <c r="F2" t="str">
+        <v>Biểu đồ mạng nhện (Radar Chart) — hiển thị nhiều thuộc tính trên trục đa hướng</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Biểu đồ bong bóng (Bubble Chart) — hiển thị mối tương quan 3 biến số</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Biểu đồ tròn (Pie Chart) — hiển thị phân bổ phần trăm cố định</v>
+      </c>
+      <c r="I2" t="str">
         <v>Biểu đồ thác nước (Waterfall Chart) — hiển thị các cột nổi biểu thị sự tăng giảm và cột chốt tổng kết</v>
       </c>
-      <c r="G2" t="str">
-        <v>Biểu đồ tròn (Pie Chart) — hiển thị phân bổ phần trăm cố định</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Biểu đồ mạng nhện (Radar Chart) — hiển thị nhiều thuộc tính trên trục đa hướng</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Biểu đồ bong bóng (Bubble Chart) — hiển thị mối tương quan 3 biến số</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>M-Code (Power Query Formula Language) dùng ở khâu chuẩn bị dữ liệu (Query Editor) để làm sạch, pivot, merge bảng trước khi load vào model. DAX (Data Analysis Expressions) dùng sau khi dữ liệu đã được load để tạo các Measures/Calculated Columns phục vụ vẽ biểu đồ.</v>
       </c>
       <c r="F3" t="str">
+        <v>M-Code chỉ chạy trên hệ điều hành MacOS; còn DAX chỉ chạy trên Windows — hệ điều hành hỗ trợ</v>
+      </c>
+      <c r="G3" t="str">
+        <v>M-Code dùng để vẽ các biểu đồ 3D phức tạp; còn DAX dùng để thiết kế màu sắc báo cáo — tính năng đồ họa</v>
+      </c>
+      <c r="H3" t="str">
+        <v>M-Code bắt buộc phải compile thành file chạy `.exe` trước khi sử dụng trong PowerBI — cơ chế biên dịch</v>
+      </c>
+      <c r="I3" t="str">
         <v>M-Code viết trong Power Query để biến đổi dữ liệu (ETL); DAX viết trong Data Model để tính toán phân tích (Data Analysis) — ETL dữ liệu đầu vào vs tính toán phân tích</v>
       </c>
-      <c r="G3" t="str">
-        <v>M-Code chỉ chạy trên hệ điều hành MacOS; còn DAX chỉ chạy trên Windows — hệ điều hành hỗ trợ</v>
-      </c>
-      <c r="H3" t="str">
-        <v>M-Code dùng để vẽ các biểu đồ 3D phức tạp; còn DAX dùng để thiết kế màu sắc báo cáo — tính năng đồ họa</v>
-      </c>
-      <c r="I3" t="str">
-        <v>M-Code bắt buộc phải compile thành file chạy `.exe` trước khi sử dụng trong PowerBI — cơ chế biên dịch</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Theo nghiên cứu hành vi đọc (Eye-tracking), mắt người dùng có xu hướng quét màn hình từ trái sang phải và từ trên xuống dưới (theo hình chữ Z hoặc F). Vì vậy, góc trên bên trái là "bất động sản vàng", nơi đặt các thông tin quan trọng nhất.</v>
       </c>
       <c r="F4" t="str">
+        <v>Ẩn sâu trong menu cài đặt cấu hình của báo cáo — menu cấu hình</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Chính giữa trung tâm của trang Dashboard — vị trí trung tâm</v>
+      </c>
+      <c r="H4" t="str">
         <v>Góc trên bên trái của trang Dashboard — tiêu điểm mắt đọc đầu tiên</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>Góc dưới cùng bên phải của trang Dashboard — vị trí kết thúc trang</v>
       </c>
-      <c r="H4" t="str">
-        <v>Chính giữa trung tâm của trang Dashboard — vị trí trung tâm</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Ẩn sâu trong menu cài đặt cấu hình của báo cáo — menu cấu hình</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
         <v>Dual-axis Chart (hoặc Line and Stacked Column Chart) cho phép hiển thị đồng thời hai biến có đơn vị và quy mô khác nhau trên cùng một trục X, giúp so sánh mối quan hệ xu hướng giữa chúng.</v>
       </c>
       <c r="F5" t="str">
+        <v>Cộng thêm 1,000,000 vào tất cả các giá trị tỷ lệ phần trăm để đưa chúng lên cùng quy mô — cộng hằng số sai lệch dữ liệu</v>
+      </c>
+      <c r="G5" t="str">
         <v>Sử dụng biểu đồ trục kép (Dual-axis / Combo Chart) với hai trục Y độc lập (trục trái cho số lượng, trục phải cho tỷ lệ) — biểu đồ trục kép</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Cộng thêm 1,000,000 vào tất cả các giá trị tỷ lệ phần trăm để đưa chúng lên cùng quy mô — cộng hằng số sai lệch dữ liệu</v>
       </c>
       <c r="H5" t="str">
         <v>Vẽ hai biểu đồ đường độc lập xếp chồng lên nhau ở hai trang báo cáo khác nhau — phân tách trang báo cáo</v>
@@ -568,7 +568,7 @@
         <v>Chuyển trục giá trị của tỷ lệ mua hàng sang thang đo logarit bắt đầu từ số âm — thang đo logarit sai quy chuẩn</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>RLS cho phép định nghĩa các bộ lọc (DAX filter) gắn với các Role. Khi người dùng đăng nhập xem báo cáo, PowerBI tự động áp bộ lọc tương ứng để lọc dữ liệu ở tầng database, đảm bảo an toàn thông tin mà chỉ cần thiết kế duy nhất một file dashboard.</v>
       </c>
       <c r="F6" t="str">
-        <v>Giới hạn dữ liệu hiển thị trên báo cáo cho từng người dùng dựa trên vai trò của họ (ví dụ: Giám đốc miền Nam chỉ xem được dữ liệu miền Nam) — bảo mật phân quyền dữ liệu theo dòng</v>
+        <v>Tự động khóa tài khoản đăng nhập của người dùng nếu họ chụp ảnh màn hình báo cáo — ngăn chặn chụp ảnh</v>
       </c>
       <c r="G6" t="str">
-        <v>Tự động khóa tài khoản đăng nhập của người dùng nếu họ chụp ảnh màn hình báo cáo — ngăn chặn chụp ảnh</v>
+        <v>Mã hóa toàn bộ các ô dữ liệu chứa số tiền giao dịch thành dạng ký tự dấu sao (*) — ẩn thông tin số tiền</v>
       </c>
       <c r="H6" t="str">
         <v>Tăng tốc độ load của các câu lệnh truy vấn dữ liệu SQL lên nhanh gấp 10 lần — tối ưu hóa tốc độ</v>
       </c>
       <c r="I6" t="str">
-        <v>Mã hóa toàn bộ các ô dữ liệu chứa số tiền giao dịch thành dạng ký tự dấu sao (*) — ẩn thông tin số tiền</v>
+        <v>Giới hạn dữ liệu hiển thị trên báo cáo cho từng người dùng dựa trên vai trò của họ (ví dụ: Giám đốc miền Nam chỉ xem được dữ liệu miền Nam) — bảo mật phân quyền dữ liệu theo dòng</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Với nhãn danh mục dài (ví dụ: "Thiết bị điện tử gia dụng"), nếu vẽ cột dọc, nhãn sẽ bị viết chéo hoặc viết dọc rất khó đọc. Biểu đồ cột ngang cung cấp không gian rộng bên trái để nhãn hiển thị thẳng thớm, dễ đọc từ trái sang phải.</v>
       </c>
       <c r="F7" t="str">
-        <v>Khi số lượng danh mục so sánh nhiều (trên 10) hoặc tên nhãn của các danh mục quá dài để hiển thị trên trục hoành — nhãn dài và số lượng danh mục lớn</v>
+        <v>Khi cần hiển thị xu hướng biến động liên tục của doanh thu theo thời gian — theo dõi xu hướng thời gian</v>
       </c>
       <c r="G7" t="str">
         <v>Khi dữ liệu so sánh chứa các giá trị số âm và số dương xen kẽ nhau — giá trị âm dương xen kẽ</v>
       </c>
       <c r="H7" t="str">
-        <v>Khi cần hiển thị xu hướng biến động liên tục của doanh thu theo thời gian — theo dõi xu hướng thời gian</v>
+        <v>Khi biểu đồ bắt buộc phải hiển thị trên màn hình tivi xoay dọc 90 độ — xoay màn hình tivi</v>
       </c>
       <c r="I7" t="str">
-        <v>Khi biểu đồ bắt buộc phải hiển thị trên màn hình tivi xoay dọc 90 độ — xoay màn hình tivi</v>
+        <v>Khi số lượng danh mục so sánh nhiều (trên 10) hoặc tên nhãn của các danh mục quá dài để hiển thị trên trục hoành — nhãn dài và số lượng danh mục lớn</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Chartjunk làm tăng tải nhận thức của người xem mà không đem lại thông tin hữu ích nào. Nguyên tắc thiết kế hiện đại hướng tới sự sạch sẽ, trực quan, loại bỏ chartjunk để dữ liệu tự lên tiếng.</v>
       </c>
       <c r="F8" t="str">
-        <v>Các yếu tố trang trí không mang giá trị thông tin dữ liệu (như hình nền lòe loẹt, viền đậm, đổ bóng 3D, họa tiết kẻ sọc) gây mất tập trung — yếu tố trang trí thừa gây nhiễu</v>
+        <v>Các câu lệnh SQL bị viết lỗi cú pháp nằm trong tệp tin nháp của lập trình viên — câu lệnh SQL nháp</v>
       </c>
       <c r="G8" t="str">
         <v>Các file báo cáo cũ đã bị xóa bỏ và nằm trong thùng rác của máy tính — file báo cáo cũ trong thùng rác</v>
       </c>
       <c r="H8" t="str">
-        <v>Các câu lệnh SQL bị viết lỗi cú pháp nằm trong tệp tin nháp của lập trình viên — câu lệnh SQL nháp</v>
+        <v>Các yếu tố trang trí không mang giá trị thông tin dữ liệu (như hình nền lòe loẹt, viền đậm, đổ bóng 3D, họa tiết kẻ sọc) gây mất tập trung — yếu tố trang trí thừa gây nhiễu</v>
       </c>
       <c r="I8" t="str">
         <v>Các biểu đồ hiển thị sai lệch số dư tài khoản thực tế của khách hàng — biểu đồ sai số liệu</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Quá nhiều màu sắc sẽ làm người dùng mất tập trung và không biết đâu là điểm nhấn. Nên sử dụng màu chủ đạo thương hiệu (Brand colors), màu trung tính (Neutral - xám, trắng) làm nền, và dùng màu tương phản mạnh (như cam, đỏ) làm điểm nhấn cho các dữ liệu bất thường.</v>
       </c>
       <c r="F9" t="str">
+        <v>Tô mỗi cột biểu đồ bằng một màu sắc ngẫu nhiên khác nhau để tạo sự sặc sỡ cuốn hút — sặc sỡ ngẫu nhiên</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Chỉ sử dụng duy nhất màu đỏ và màu xanh lá cây cho toàn bộ các biểu đồ trên dashboard — giới hạn đỏ xanh</v>
+      </c>
+      <c r="H9" t="str">
         <v>Sử dụng tối đa 3-5 màu sắc trong một bảng màu nhất quán, kết hợp các sắc độ đậm nhạt (Saturation/Value) của cùng một màu để phân biệt dữ liệu — bảng màu nhất quán giới hạn</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Tô mỗi cột biểu đồ bằng một màu sắc ngẫu nhiên khác nhau để tạo sự sặc sỡ cuốn hút — sặc sỡ ngẫu nhiên</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Chỉ sử dụng duy nhất màu đỏ và màu xanh lá cây cho toàn bộ các biểu đồ trên dashboard — giới hạn đỏ xanh</v>
       </c>
       <c r="I9" t="str">
         <v>Sử dụng các màu sắc phản quang (Neon) trên nền đen để tạo hiệu ứng phát sáng — màu phản quang</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,10 +716,10 @@
         <v>Import Mode nén dữ liệu cực tốt và chạy rất nhanh trên bộ nhớ RAM (VertiPaq engine) nhưng dung lượng file bị giới hạn (1GB cho bản Pro) và cần thiết lập lịch làm mới (Refresh schedule). DirectQuery không giới hạn dung lượng file báo cáo và cập nhật dữ liệu real-time, nhưng hiệu năng phụ thuộc hoàn toàn vào tốc độ của database nguồn.</v>
       </c>
       <c r="F10" t="str">
+        <v>Import chỉ hỗ trợ kết nối với file Excel; DirectQuery chỉ hỗ trợ kết nối với cơ sở dữ liệu MySQL — phân loại nguồn kết nối</v>
+      </c>
+      <c r="G10" t="str">
         <v>Import: Nạp toàn bộ dữ liệu vào bộ nhớ trong của PowerBI (nhanh, tốn RAM); DirectQuery: Không nạp dữ liệu, truy vấn trực tiếp từ database nguồn mỗi khi tương tác biểu đồ (chậm hơn, dữ liệu thời gian thực) — nạp bộ nhớ vs truy vấn trực tiếp thời gian thực</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Import chỉ hỗ trợ kết nối với file Excel; DirectQuery chỉ hỗ trợ kết nối với cơ sở dữ liệu MySQL — phân loại nguồn kết nối</v>
       </c>
       <c r="H10" t="str">
         <v>Import bắt buộc phải có tài khoản VIP của Microsoft; DirectQuery hoàn toàn miễn phí cho tất cả mọi người — chi phí bản quyền</v>
@@ -728,7 +728,7 @@
         <v>Import tự động mã hóa dữ liệu; DirectQuery tự động xóa dữ liệu trùng lặp khi nạp — cơ chế tự động dữ liệu</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Choropleth Map (Bản đồ phân bậc màu) sử dụng các sắc độ của một màu (ví dụ: xám nhạt đến xanh đậm) tô lên các ranh giới hành chính để thể hiện mật độ dữ liệu (ví dụ: mật độ dân số, tỷ lệ thất nghiệp theo tỉnh).</v>
       </c>
       <c r="F11" t="str">
+        <v>Vẽ các đường nối ngoằn ngoèo thể hiện luồng đi của hàng hóa giữa các quốc gia — biểu đồ luồng giao thông</v>
+      </c>
+      <c r="G11" t="str">
         <v>Tô màu các khu vực địa lý dựa trên thang độ đậm nhạt tương ứng với giá trị số liệu đo lường tại khu vực đó — tô màu theo cường độ giá trị</v>
       </c>
-      <c r="G11" t="str">
-        <v>Vẽ các đường nối ngoằn ngoèo thể hiện luồng đi của hàng hóa giữa các quốc gia — biểu đồ luồng giao thông</v>
-      </c>
       <c r="H11" t="str">
+        <v>Tự động hiển thị sơ đồ đường đi ngắn nhất giữa hai địa điểm trên bản đồ Google Maps — định vị đường đi ngắn nhất</v>
+      </c>
+      <c r="I11" t="str">
         <v>Hiển thị các chấm tròn có kích thước to nhỏ khác nhau tại tọa độ của các thành phố — biểu đồ chấm tròn tọa độ</v>
       </c>
-      <c r="I11" t="str">
-        <v>Tự động hiển thị sơ đồ đường đi ngắn nhất giữa hai địa điểm trên bản đồ Google Maps — định vị đường đi ngắn nhất</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
